--- a/api/templates/report_custom_fields_completion/en.xlsx
+++ b/api/templates/report_custom_fields_completion/en.xlsx
@@ -167,12 +167,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -616,13 +621,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:1" s="5" customFormat="1" ht="58.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
     </row>

--- a/api/templates/report_custom_fields_completion/en.xlsx
+++ b/api/templates/report_custom_fields_completion/en.xlsx
@@ -27,12 +27,6 @@
     <t>Dates: &lt;Dates&gt;</t>
   </si>
   <si>
-    <t>States: &lt;States&gt;</t>
-  </si>
-  <si>
-    <t>LGA: &lt;Lgas&gt;</t>
-  </si>
-  <si>
     <t>Percent of custom fields completion for the MTB form</t>
   </si>
   <si>
@@ -40,6 +34,12 @@
   </si>
   <si>
     <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
   </si>
 </sst>
 </file>
@@ -595,7 +595,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
@@ -605,12 +605,12 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
@@ -623,12 +623,12 @@
     </row>
     <row r="7" spans="1:1" s="5" customFormat="1" ht="58.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
